--- a/branches/fix/go-publish-bootstrap/observations-summary.xlsx
+++ b/branches/fix/go-publish-bootstrap/observations-summary.xlsx
@@ -86,7 +86,7 @@
     <t>MII PR Biobank Observation Morphologie</t>
   </si>
   <si>
-    <t>Phenotypic Quality Ontology#PATO:0010006</t>
+    <t>pato.owl#PATO:0010006</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
